--- a/Timeline_Template.xlsx
+++ b/Timeline_Template.xlsx
@@ -1,42 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2366920\Documents\Gerador Proposta\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6033792D-E4BE-4B92-9B3F-647A255CC577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Timeline" sheetId="1" r:id="rId1"/>
-    <sheet name="Rate Card" sheetId="2" r:id="rId2"/>
-    <sheet name="Alt format (list)" sheetId="3" r:id="rId3"/>
-    <sheet name="Instructions" sheetId="4" r:id="rId4"/>
+    <sheet sheetId="1" name="Timeline" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Rate Card" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Alt format (list)" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Instructions" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="55">
   <si>
     <t>Phase</t>
   </si>
@@ -152,12 +130,24 @@
     <t>Y</t>
   </si>
   <si>
+    <t>Total FTE</t>
+  </si>
+  <si>
+    <t>Insira novas linhas ACIMA da linha "Total FTE" (a linha Total é ignorada na importação).</t>
+  </si>
+  <si>
     <t>Cost/h</t>
   </si>
   <si>
     <t>Rate/h</t>
   </si>
   <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Valor ilustrativo — substitua pelo rate card oficial</t>
+  </si>
+  <si>
     <t>Start</t>
   </si>
   <si>
@@ -173,43 +163,68 @@
     <t>Build</t>
   </si>
   <si>
-    <t>How to use</t>
-  </si>
-  <si>
-    <t>1. Fill the "Timeline" sheet: one row per Phase + Role, FTE allocation per sprint (SP1, SP2…). Use W1, W2… for weekly plans.</t>
-  </si>
-  <si>
-    <t>2. Mark optional scope with "Y" in the Optional column.</t>
-  </si>
-  <si>
-    <t>3. Fill the "Rate Card" sheet with Cost/h and/or Rate/h (net of taxes).</t>
-  </si>
-  <si>
-    <t>4. Upload the file in the app. Rates in this template are illustrative only.</t>
-  </si>
-  <si>
-    <t>Alternative: list format with Start / End / FTE (see "Alt format (list)").</t>
+    <t>How to use / Como usar</t>
+  </si>
+  <si>
+    <t>1. Timeline: uma linha por Fase + Perfil; FTE por sprint (SP1, SP2…). Use W1, W2… para planos semanais.</t>
+  </si>
+  <si>
+    <t>2. Marque o escopo opcional com "Y" na coluna Optional.</t>
+  </si>
+  <si>
+    <t>3. Rate Card: preencha Cost/h e/ou Rate/h (líquidos de impostos). A aba é importada automaticamente.</t>
+  </si>
+  <si>
+    <t>4. Carregue este arquivo no app (aba 1). As propostas geradas pelo app são salvas em outro .xlsx, que o app também reabre.</t>
+  </si>
+  <si>
+    <t>Formato alternativo: lista com Start / End / FTE (aba "Alt format (list)").</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF5F6B7A"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B2545"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -224,14 +239,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -564,76 +590,75 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R17"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32.875" customWidth="1"/>
-    <col min="2" max="2" width="16.875" customWidth="1"/>
-    <col min="3" max="3" width="26.875" customWidth="1"/>
-    <col min="4" max="4" width="7.875" customWidth="1"/>
-    <col min="5" max="5" width="10.875" customWidth="1"/>
-    <col min="6" max="6" width="9.875" customWidth="1"/>
-    <col min="7" max="18" width="6.875" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="7" max="18" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -658,38 +683,8 @@
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" t="s">
-        <v>19</v>
-      </c>
-      <c r="P2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>19</v>
-      </c>
-      <c r="R2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -714,38 +709,8 @@
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N3" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P3" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>19</v>
-      </c>
-      <c r="R3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -770,38 +735,8 @@
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="I4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" t="s">
-        <v>19</v>
-      </c>
-      <c r="N4" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4" t="s">
-        <v>19</v>
-      </c>
-      <c r="P4" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>19</v>
-      </c>
-      <c r="R4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -820,12 +755,6 @@
       <c r="F5" t="s">
         <v>19</v>
       </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
-      </c>
       <c r="I5">
         <v>2</v>
       </c>
@@ -844,20 +773,8 @@
       <c r="N5">
         <v>2</v>
       </c>
-      <c r="O5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P5" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>19</v>
-      </c>
-      <c r="R5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -876,12 +793,6 @@
       <c r="F6" t="s">
         <v>19</v>
       </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s">
-        <v>19</v>
-      </c>
       <c r="I6">
         <v>0.5</v>
       </c>
@@ -900,20 +811,8 @@
       <c r="N6">
         <v>0.5</v>
       </c>
-      <c r="O6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P6" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>19</v>
-      </c>
-      <c r="R6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -932,18 +831,6 @@
       <c r="F7" t="s">
         <v>19</v>
       </c>
-      <c r="G7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" t="s">
-        <v>19</v>
-      </c>
       <c r="K7">
         <v>2</v>
       </c>
@@ -962,14 +849,8 @@
       <c r="P7">
         <v>2</v>
       </c>
-      <c r="Q7" t="s">
-        <v>19</v>
-      </c>
-      <c r="R7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -988,44 +869,14 @@
       <c r="F8" t="s">
         <v>19</v>
       </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" t="s">
-        <v>19</v>
-      </c>
-      <c r="L8" t="s">
-        <v>19</v>
-      </c>
-      <c r="M8" t="s">
-        <v>19</v>
-      </c>
-      <c r="N8" t="s">
-        <v>19</v>
-      </c>
       <c r="O8">
         <v>1</v>
       </c>
       <c r="P8">
         <v>1</v>
       </c>
-      <c r="Q8" t="s">
-        <v>19</v>
-      </c>
-      <c r="R8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1044,18 +895,6 @@
       <c r="F9" t="s">
         <v>19</v>
       </c>
-      <c r="G9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" t="s">
-        <v>19</v>
-      </c>
       <c r="K9">
         <v>0.5</v>
       </c>
@@ -1074,14 +913,8 @@
       <c r="P9">
         <v>0.5</v>
       </c>
-      <c r="Q9" t="s">
-        <v>19</v>
-      </c>
-      <c r="R9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1100,30 +933,6 @@
       <c r="F10" t="s">
         <v>19</v>
       </c>
-      <c r="G10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" t="s">
-        <v>19</v>
-      </c>
-      <c r="I10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" t="s">
-        <v>19</v>
-      </c>
-      <c r="K10" t="s">
-        <v>19</v>
-      </c>
-      <c r="L10" t="s">
-        <v>19</v>
-      </c>
-      <c r="M10" t="s">
-        <v>19</v>
-      </c>
-      <c r="N10" t="s">
-        <v>19</v>
-      </c>
       <c r="O10">
         <v>1</v>
       </c>
@@ -1133,11 +942,8 @@
       <c r="Q10">
         <v>1</v>
       </c>
-      <c r="R10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1156,44 +962,11 @@
       <c r="F11" t="s">
         <v>19</v>
       </c>
-      <c r="G11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" t="s">
-        <v>19</v>
-      </c>
-      <c r="L11" t="s">
-        <v>19</v>
-      </c>
-      <c r="M11" t="s">
-        <v>19</v>
-      </c>
-      <c r="N11" t="s">
-        <v>19</v>
-      </c>
-      <c r="O11" t="s">
-        <v>19</v>
-      </c>
-      <c r="P11" t="s">
-        <v>19</v>
-      </c>
       <c r="Q11">
         <v>1</v>
       </c>
-      <c r="R11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1212,44 +985,11 @@
       <c r="F12" t="s">
         <v>19</v>
       </c>
-      <c r="G12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J12" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L12" t="s">
-        <v>19</v>
-      </c>
-      <c r="M12" t="s">
-        <v>19</v>
-      </c>
-      <c r="N12" t="s">
-        <v>19</v>
-      </c>
-      <c r="O12" t="s">
-        <v>19</v>
-      </c>
-      <c r="P12" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>19</v>
-      </c>
       <c r="R12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -1268,12 +1008,6 @@
       <c r="F13" t="s">
         <v>19</v>
       </c>
-      <c r="G13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" t="s">
-        <v>19</v>
-      </c>
       <c r="I13">
         <v>0.5</v>
       </c>
@@ -1305,7 +1039,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -1324,36 +1058,6 @@
       <c r="F14" t="s">
         <v>37</v>
       </c>
-      <c r="G14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" t="s">
-        <v>19</v>
-      </c>
-      <c r="L14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M14" t="s">
-        <v>19</v>
-      </c>
-      <c r="N14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O14" t="s">
-        <v>19</v>
-      </c>
-      <c r="P14" t="s">
-        <v>19</v>
-      </c>
       <c r="Q14">
         <v>2</v>
       </c>
@@ -1361,43 +1065,125 @@
         <v>2</v>
       </c>
     </row>
+    <row r="15" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="3">
+        <f>SUM(G2:G14)</f>
+      </c>
+      <c r="H15" s="3">
+        <f>SUM(H2:H14)</f>
+      </c>
+      <c r="I15" s="3">
+        <f>SUM(I2:I14)</f>
+      </c>
+      <c r="J15" s="3">
+        <f>SUM(J2:J14)</f>
+      </c>
+      <c r="K15" s="3">
+        <f>SUM(K2:K14)</f>
+      </c>
+      <c r="L15" s="3">
+        <f>SUM(L2:L14)</f>
+      </c>
+      <c r="M15" s="3">
+        <f>SUM(M2:M14)</f>
+      </c>
+      <c r="N15" s="3">
+        <f>SUM(N2:N14)</f>
+      </c>
+      <c r="O15" s="3">
+        <f>SUM(O2:O14)</f>
+      </c>
+      <c r="P15" s="3">
+        <f>SUM(P2:P14)</f>
+      </c>
+      <c r="Q15" s="3">
+        <f>SUM(Q2:Q14)</f>
+      </c>
+      <c r="R15" s="3">
+        <f>SUM(R2:R14)</f>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="G2:R14">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF7FA8D8"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Optional" error="Use Y (opcional) ou deixe vazio." sqref="F2:F54">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorTitle="FTE" error="Informe a alocação em FTE (ex.: 1, 0,5)." sqref="G2:R54">
+      <formula1>0</formula1>
+      <formula2>50</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:R14" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="26.875" customWidth="1"/>
-    <col min="2" max="2" width="7.875" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="5" width="9.875" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="5" width="10" style="5" customWidth="1"/>
+    <col min="6" max="6" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -1407,14 +1193,17 @@
       <c r="C2" t="s">
         <v>22</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="5">
         <v>170</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="5">
         <v>260</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1424,14 +1213,17 @@
       <c r="C3" t="s">
         <v>22</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="5">
         <v>185</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="5">
         <v>280</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -1441,14 +1233,17 @@
       <c r="C4" t="s">
         <v>22</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="5">
         <v>125</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="5">
         <v>190</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -1458,14 +1253,17 @@
       <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="5">
         <v>130</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="5">
         <v>200</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1475,14 +1273,17 @@
       <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="5">
         <v>130</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="5">
         <v>200</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -1492,14 +1293,17 @@
       <c r="C7" t="s">
         <v>22</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="5">
         <v>90</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="5">
         <v>140</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -1509,55 +1313,64 @@
       <c r="C8" t="s">
         <v>22</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="5">
         <v>125</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="5">
         <v>190</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:E8" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="7" width="8" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
@@ -1581,9 +1394,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
         <v>27</v>
@@ -1609,54 +1422,50 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:H3" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="110.875" customWidth="1"/>
+    <col min="1" max="1" width="120" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:A6" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>